--- a/Simulation/Results/p.rand_Censor.Ints_mean.surv.70.xlsx
+++ b/Simulation/Results/p.rand_Censor.Ints_mean.surv.70.xlsx
@@ -47,16 +47,16 @@
     <t xml:space="preserve">rand</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1 mins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3 mins</t>
+    <t xml:space="preserve">5.6 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2 mins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5 mins</t>
   </si>
 </sst>
 </file>
@@ -419,13 +419,13 @@
         <v>50</v>
       </c>
       <c r="B2" t="n">
-        <v>0.05</v>
+        <v>0.0519</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0524</v>
+        <v>0.0549</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0535</v>
+        <v>0.0513</v>
       </c>
       <c r="E2" t="n">
         <v>0.0142857142857143</v>
@@ -448,13 +448,13 @@
         <v>100</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0465</v>
+        <v>0.0438</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0562</v>
+        <v>0.05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0527</v>
+        <v>0.0534</v>
       </c>
       <c r="E3" t="n">
         <v>0.0142857142857143</v>
@@ -477,13 +477,13 @@
         <v>200</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0521</v>
+        <v>0.0501</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0526</v>
+        <v>0.0494</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0509</v>
+        <v>0.0484</v>
       </c>
       <c r="E4" t="n">
         <v>0.0142857142857143</v>
@@ -506,13 +506,13 @@
         <v>500</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0494</v>
+        <v>0.0488</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0499</v>
+        <v>0.0509</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0493</v>
+        <v>0.0503</v>
       </c>
       <c r="E5" t="n">
         <v>0.0142857142857143</v>
